--- a/artfynd/A 63537-2025 artfynd.xlsx
+++ b/artfynd/A 63537-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87865976</v>
+        <v>87865798</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497022.2948968325</v>
+        <v>497014</v>
       </c>
       <c r="R2" t="n">
-        <v>6594226.004989851</v>
+        <v>6594274</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-09-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>87865740</v>
       </c>
       <c r="B3" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497022.2948968325</v>
+        <v>497022</v>
       </c>
       <c r="R3" t="n">
-        <v>6594226.004989851</v>
+        <v>6594226</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +849,9 @@
           <t>2020-09-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,6 +881,643 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87865976</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>497022</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6594226</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>87865977</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>497006</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6594365</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87865943</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497006</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6594365</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88166627</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497003</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6594351</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87865683</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>497006</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6594365</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88166394</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497003</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6594351</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 63537-2025 artfynd.xlsx
+++ b/artfynd/A 63537-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,45 +888,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87865976</v>
+        <v>135448708</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>108274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>220102</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Vinterskogstorp, Vinterskogstorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497022</v>
+        <v>497096</v>
       </c>
       <c r="R4" t="n">
-        <v>6594226</v>
+        <v>6594328</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -953,12 +953,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,32 +979,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Camilla Pettersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Camilla Pettersson, Anders Carlberg, Kjell Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87865977</v>
+        <v>87865976</v>
       </c>
       <c r="B5" t="n">
         <v>106813</v>
@@ -1029,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497006</v>
+        <v>497022</v>
       </c>
       <c r="R5" t="n">
-        <v>6594365</v>
+        <v>6594226</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87865943</v>
+        <v>87865977</v>
       </c>
       <c r="B6" t="n">
-        <v>101326</v>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88166627</v>
+        <v>87865943</v>
       </c>
       <c r="B7" t="n">
         <v>101326</v>
@@ -1241,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497003</v>
+        <v>497006</v>
       </c>
       <c r="R7" t="n">
-        <v>6594351</v>
+        <v>6594365</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1271,12 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,7 +1291,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1312,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87865683</v>
+        <v>88166627</v>
       </c>
       <c r="B8" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1324,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497006</v>
+        <v>497003</v>
       </c>
       <c r="R8" t="n">
-        <v>6594365</v>
+        <v>6594351</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1377,12 +1378,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,7 +1397,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1418,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88166394</v>
+        <v>87865683</v>
       </c>
       <c r="B9" t="n">
         <v>101228</v>
@@ -1453,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497003</v>
+        <v>497006</v>
       </c>
       <c r="R9" t="n">
-        <v>6594351</v>
+        <v>6594365</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,12 +1484,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,13 +1498,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1518,6 +1518,113 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88166394</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497003</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6594351</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 63537-2025 artfynd.xlsx
+++ b/artfynd/A 63537-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865740</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448708</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865976</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865977</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865943</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88166627</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865683</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,8 +1674,24 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88166394</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63537-2025 artfynd.xlsx
+++ b/artfynd/A 63537-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>135448708</v>
       </c>
       <c r="B4" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63537-2025 artfynd.xlsx
+++ b/artfynd/A 63537-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>135448708</v>
       </c>
       <c r="B4" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63537-2025 artfynd.xlsx
+++ b/artfynd/A 63537-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,45 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87865976</v>
+        <v>135448708</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>108362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>220102</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Vinterskogstorp, Vinterskogstorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497022</v>
+        <v>497096</v>
       </c>
       <c r="R4" t="n">
-        <v>6594226</v>
+        <v>6594328</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,12 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,37 +994,28 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Camilla Pettersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Camilla Pettersson, Anders Carlberg, Kjell Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87865976</t>
+          <t>https://artportalen.se/Sighting/135448708</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87865977</v>
+        <v>87865976</v>
       </c>
       <c r="B5" t="n">
         <v>106813</v>
@@ -1049,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497006</v>
+        <v>497022</v>
       </c>
       <c r="R5" t="n">
-        <v>6594365</v>
+        <v>6594226</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,38 +1120,38 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87865977</t>
+          <t>https://artportalen.se/Sighting/87865976</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87865943</v>
+        <v>87865977</v>
       </c>
       <c r="B6" t="n">
-        <v>101326</v>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1230,13 +1231,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87865943</t>
+          <t>https://artportalen.se/Sighting/87865977</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88166627</v>
+        <v>87865943</v>
       </c>
       <c r="B7" t="n">
         <v>101326</v>
@@ -1271,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497003</v>
+        <v>497006</v>
       </c>
       <c r="R7" t="n">
-        <v>6594351</v>
+        <v>6594365</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1301,12 +1302,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1321,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1341,16 +1342,16 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88166627</t>
+          <t>https://artportalen.se/Sighting/87865943</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87865683</v>
+        <v>88166627</v>
       </c>
       <c r="B8" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497006</v>
+        <v>497003</v>
       </c>
       <c r="R8" t="n">
-        <v>6594365</v>
+        <v>6594351</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,12 +1413,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,7 +1432,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,13 +1453,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87865683</t>
+          <t>https://artportalen.se/Sighting/88166627</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88166394</v>
+        <v>87865683</v>
       </c>
       <c r="B9" t="n">
         <v>101228</v>
@@ -1493,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497003</v>
+        <v>497006</v>
       </c>
       <c r="R9" t="n">
-        <v>6594351</v>
+        <v>6594365</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,12 +1524,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,13 +1538,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,6 +1563,118 @@
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865683</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88166394</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497003</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6594351</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/88166394</t>
         </is>
@@ -1578,6 +1690,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63537-2025 artfynd.xlsx
+++ b/artfynd/A 63537-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>135448708</v>
       </c>
       <c r="B4" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63537-2025 artfynd.xlsx
+++ b/artfynd/A 63537-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>135448708</v>
       </c>
       <c r="B4" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
